--- a/docs/0OMsoqOg9GiJ2xusVHM2/.gitbook/assets/IO - Template servizi - Scuola primaria e secondaria.xlsx
+++ b/docs/0OMsoqOg9GiJ2xusVHM2/.gitbook/assets/IO - Template servizi - Scuola primaria e secondaria.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="277" uniqueCount="160">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="277" uniqueCount="158">
   <si>
     <r>
       <t xml:space="preserve">
@@ -192,7 +192,7 @@
     <t>Utilizza il testo indicato per il pulsante. Inserisci il link alla pagina web che rimanda al servizio.</t>
   </si>
   <si>
-    <t>Vedi iscrizioni aperte</t>
+    <t>Consulta iscrizioni aperte</t>
   </si>
   <si>
     <t>Link a termini e condizioni d'uso</t>
@@ -722,7 +722,7 @@
         <sz val="10"/>
         <rFont val="Titillium Web"/>
       </rPr>
-      <t xml:space="preserve">  per l’anno educativo </t>
+      <t xml:space="preserve"> per l’anno educativo </t>
     </r>
     <r>
       <rPr>
@@ -739,7 +739,7 @@
         <sz val="10"/>
         <rFont val="Titillium Web"/>
       </rPr>
-      <t xml:space="preserve">. 
+      <t xml:space="preserve">.
 </t>
     </r>
     <r>
@@ -1000,7 +1000,7 @@
         <sz val="10"/>
         <rFont val="Titillium Web"/>
       </rPr>
-      <t xml:space="preserve">. 
+      <t xml:space="preserve">.
 Sarà possibile consultare la propria posizione in graduatoria dal </t>
     </r>
     <r>
@@ -1131,7 +1131,7 @@
         <sz val="10"/>
         <rFont val="Titillium Web"/>
       </rPr>
-      <t xml:space="preserve"> non è stata accolta. 
+      <t xml:space="preserve"> non è stata accolta.
 Per ulteriori informazioni, [visita questo sito](URL).</t>
     </r>
   </si>
@@ -1860,7 +1860,7 @@
         <sz val="10"/>
         <rFont val="Titillium Web"/>
       </rPr>
-      <t xml:space="preserve"> non è stata accolta. 
+      <t xml:space="preserve"> non è stata accolta.
 Per ulteriori informazioni, [visita il sito](URL).</t>
     </r>
   </si>
@@ -2184,6 +2184,9 @@
     <t>Vai alla tua domanda</t>
   </si>
   <si>
+    <t>Aggiungi documenti</t>
+  </si>
+  <si>
     <t>-</t>
   </si>
   <si>
@@ -2193,10 +2196,7 @@
     <t>Paga (inserito automaticamente dall'app se il messaggio prevede un avviso di pagamento pagoPA)</t>
   </si>
   <si>
-    <t>Vedi ricevuta</t>
-  </si>
-  <si>
-    <t>Vedi Avviso</t>
+    <t>Vai alla ricevuta</t>
   </si>
   <si>
     <r>
@@ -2216,7 +2216,7 @@
       <rPr>
         <b/>
       </rPr>
-      <t>Allegato (Premium)</t>
+      <t>Allegato</t>
     </r>
     <r>
       <rPr/>
@@ -2335,14 +2335,6 @@
       </rPr>
       <t>Note aggiuntive</t>
     </r>
-  </si>
-  <si>
-    <t>✨ Messaggio Premium — Se hai un contratto Premium, ti consigliamo di configurare questo messaggio con promemoria Premium: i destinatari verranno avvisati dell‘avvicinarsi della scadenza tramite notifica push.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Promemoria automatici — Messaggi Premium
-Impostando il messaggio di Avviso di pagamento come Messaggio Premium, disponibile a seconda della tipologia di contratto sottoscritto dall’ente, non è necessario inviare il seguente messaggio di promemoria.
-Gli utenti che hanno dato il loro consenso, infatti, riceveranno automaticamente una notifica push sui loro dispositivi all’avvicinarsi della scadenza.</t>
   </si>
   <si>
     <t xml:space="preserve">Mancato pagamento
@@ -3224,49 +3216,49 @@
         <v>121</v>
       </c>
       <c r="E6" s="34" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="F6" s="34" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="G6" s="34" t="s">
+        <v>123</v>
+      </c>
+      <c r="H6" s="34" t="s">
+        <v>124</v>
+      </c>
+      <c r="I6" s="34" t="s">
+        <v>124</v>
+      </c>
+      <c r="J6" s="34" t="s">
+        <v>124</v>
+      </c>
+      <c r="K6" s="34" t="s">
+        <v>124</v>
+      </c>
+      <c r="L6" s="34" t="s">
         <v>122</v>
       </c>
-      <c r="H6" s="34" t="s">
-        <v>123</v>
-      </c>
-      <c r="I6" s="34" t="s">
-        <v>123</v>
-      </c>
-      <c r="J6" s="34" t="s">
-        <v>123</v>
-      </c>
-      <c r="K6" s="34" t="s">
-        <v>123</v>
-      </c>
-      <c r="L6" s="34" t="s">
-        <v>121</v>
-      </c>
       <c r="M6" s="34" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="N6" s="34" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="O6" s="34" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="P6" s="34" t="s">
+        <v>125</v>
+      </c>
+      <c r="Q6" s="34" t="s">
         <v>124</v>
       </c>
-      <c r="Q6" s="34" t="s">
-        <v>125</v>
-      </c>
       <c r="R6" s="34" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="S6" s="34" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.25">
@@ -3333,58 +3325,58 @@
         <v>127</v>
       </c>
       <c r="B8" s="34" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C8" s="34" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D8" s="34" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="E8" s="34" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="F8" s="34" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="G8" s="34" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="H8" s="34" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="I8" s="34" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="J8" s="34" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="K8" s="34" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="L8" s="34" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="M8" s="34" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="N8" s="34" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="O8" s="34" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="P8" s="34" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="Q8" s="34" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="R8" s="34" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="S8" s="34" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="9" spans="1:19" x14ac:dyDescent="0.25">
@@ -3528,13 +3520,13 @@
         <v>68</v>
       </c>
       <c r="H11" s="34" t="s">
-        <v>157</v>
+        <v>68</v>
       </c>
       <c r="I11" s="34" t="s">
-        <v>158</v>
+        <v>68</v>
       </c>
       <c r="J11" s="34" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="K11" s="34" t="s">
         <v>68</v>
